--- a/Matricula_5to_grado.xlsx
+++ b/Matricula_5to_grado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45896CA2-7336-4ED9-B37E-76F79EFAFAD3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF95052-17D9-41E8-B094-4B9B0B9844D3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="134">
   <si>
     <t xml:space="preserve">APELLIDOS </t>
   </si>
@@ -218,51 +218,6 @@
     <t>F</t>
   </si>
   <si>
-    <t xml:space="preserve">PARRA INGRID DEL VALLE </t>
-  </si>
-  <si>
-    <t>CASTILLO RANGEL LISBETH JAKELINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRIOS CALDERON CARLA ANDREINA </t>
-  </si>
-  <si>
-    <t>GOMEZ XIOMARA CORORMOTO</t>
-  </si>
-  <si>
-    <t>PARRA PARRA VIRGINIA YENIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TREJO AVENDAÑO MARIA ANDREINA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRIOS ZERPA MARIA MONICA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALARCON QUINTERO DINARDY </t>
-  </si>
-  <si>
-    <t>TREJO GIL JAIME ALCIDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORIN MILAGROS </t>
-  </si>
-  <si>
-    <t>SUAREZ PEÑA DENNIS MARIELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARRA SUESCUN YECENIA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANCHEZ ANA TERESA </t>
-  </si>
-  <si>
-    <t>BRICEÑO QUINTERO LUISA</t>
-  </si>
-  <si>
-    <t>RANGEL CASTILLO NORY</t>
-  </si>
-  <si>
     <t xml:space="preserve">AVENDAÑO GOMEZ YONELA </t>
   </si>
   <si>
@@ -284,9 +239,6 @@
     <t>SAN PEDRO</t>
   </si>
   <si>
-    <t xml:space="preserve">ALDANA PARRA MARIA </t>
-  </si>
-  <si>
     <t>ALBERTO CARNEVALI</t>
   </si>
   <si>
@@ -375,13 +327,115 @@
   </si>
   <si>
     <t>0412-3891442</t>
+  </si>
+  <si>
+    <t>APELLIDO DEL REPRESENTANTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INGRID DEL VALLE </t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LISBETH JAKELINE</t>
+  </si>
+  <si>
+    <t>CASTILLO RANGEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CARLA ANDREINA </t>
+  </si>
+  <si>
+    <t>BARRIOS CALDERON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOMEZ </t>
+  </si>
+  <si>
+    <t>XIOMARA CORORMOTO</t>
+  </si>
+  <si>
+    <t>VIRGINIA YENIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARRA PARRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA ANDREINA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREJO AVENDAÑO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDANA PARRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA MONICA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRIOS ZERPA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DINARDY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALARCON QUINTERO </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JAIME ALCIDES</t>
+  </si>
+  <si>
+    <t>TREJO GIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILAGROS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORIN </t>
+  </si>
+  <si>
+    <t>DENNIS MARIELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUAREZ PEÑA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> YECENIA </t>
+  </si>
+  <si>
+    <t>PARRA SUESCUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA TERESA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANCHEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LUISA</t>
+  </si>
+  <si>
+    <t>BRICEÑO QUINTERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NORY</t>
+  </si>
+  <si>
+    <t>RANGEL CASTILLO</t>
+  </si>
+  <si>
+    <t>AVENDAÑO GOMEZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +461,14 @@
     </font>
     <font>
       <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,7 +609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -588,6 +650,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -597,17 +678,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -860,7 +938,7 @@
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
@@ -1192,40 +1270,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:Q29"/>
+  <dimension ref="A4:W30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="8" width="4.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="35.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="37.140625" customWidth="1"/>
-    <col min="17" max="17" width="34.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="2.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="4.7109375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="2.7109375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="32.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="40.5703125" customWidth="1"/>
+    <col min="19" max="19" width="18.5703125" customWidth="1"/>
+    <col min="20" max="20" width="17.28515625" customWidth="1"/>
+    <col min="21" max="21" width="24.28515625" customWidth="1"/>
+    <col min="22" max="22" width="37.140625" customWidth="1"/>
+    <col min="23" max="23" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1241,65 +1326,77 @@
         <v>18</v>
       </c>
       <c r="K6" s="13"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="14"/>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="16" t="s">
+      <c r="H8" s="26"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="N8" s="16" t="s">
+      <c r="S8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="U8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="V8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
+      <c r="W8" s="3"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
       <c r="B9" s="15"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17" t="s">
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22" t="s">
         <v>57</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -1311,18 +1408,26 @@
       <c r="I9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
       <c r="L9" s="17"/>
-      <c r="M9" s="17">
-        <v>19421428</v>
-      </c>
+      <c r="M9" s="17"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q9" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22">
+        <v>19421428</v>
+      </c>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="3"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>1</v>
       </c>
@@ -1354,19 +1459,27 @@
       <c r="K10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="S10" s="6">
         <v>13648370</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T10" s="6"/>
+      <c r="U10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="V10" s="8"/>
+    </row>
+    <row r="11" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>2</v>
       </c>
@@ -1392,29 +1505,37 @@
       <c r="I11" s="6">
         <v>2014</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="31">
         <v>10</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11" s="6">
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="S11" s="6">
         <v>18310473</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P11" s="8" t="s">
+      <c r="T11" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>3</v>
       </c>
@@ -1446,23 +1567,31 @@
       <c r="K12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S12" s="6">
         <v>11955213</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>4</v>
       </c>
@@ -1494,23 +1623,31 @@
       <c r="K13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" s="6">
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="S13" s="6">
         <v>25560862</v>
       </c>
-      <c r="N13" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>5</v>
       </c>
@@ -1542,23 +1679,31 @@
       <c r="K14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14" s="6">
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S14" s="6">
         <v>22655606</v>
       </c>
-      <c r="N14" s="6">
+      <c r="T14" s="6">
         <v>4120296760</v>
       </c>
-      <c r="O14" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>6</v>
       </c>
@@ -1590,22 +1735,30 @@
       <c r="K15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="S15" s="6">
+        <v>22655626</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="U15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="6">
-        <v>22655626</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="10"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V15" s="8"/>
+      <c r="W15" s="10"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>7</v>
       </c>
@@ -1637,23 +1790,31 @@
       <c r="K16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M16" s="6">
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="S16" s="6">
         <v>20434036</v>
       </c>
-      <c r="N16" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>8</v>
       </c>
@@ -1685,23 +1846,31 @@
       <c r="K17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M17" s="6">
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="S17" s="6">
         <v>25643421</v>
       </c>
-      <c r="N17" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>9</v>
       </c>
@@ -1733,23 +1902,31 @@
       <c r="K18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="S18" s="6">
+        <v>11460128</v>
+      </c>
+      <c r="T18" s="6">
+        <v>4125494832</v>
+      </c>
+      <c r="U18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M18" s="6">
-        <v>11460128</v>
-      </c>
-      <c r="N18" s="6">
-        <v>4125494832</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V18" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>10</v>
       </c>
@@ -1781,23 +1958,31 @@
       <c r="K19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L19" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M19" s="6">
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="R19" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="S19" s="6">
         <v>12123839</v>
       </c>
-      <c r="N19" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>11</v>
       </c>
@@ -1829,23 +2014,31 @@
       <c r="K20" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M20" s="6">
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="R20" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S20" s="6">
         <v>22655269</v>
       </c>
-      <c r="N20" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="U20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>12</v>
       </c>
@@ -1877,23 +2070,31 @@
       <c r="K21" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L21" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M21" s="6">
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="R21" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="S21" s="6">
         <v>17130994</v>
       </c>
-      <c r="N21" s="6">
+      <c r="T21" s="6">
         <v>4127693370</v>
       </c>
-      <c r="O21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U21" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>13</v>
       </c>
@@ -1925,23 +2126,31 @@
       <c r="K22" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="M22" s="6">
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="R22" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="S22" s="6">
         <v>17340678</v>
       </c>
-      <c r="N22" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>14</v>
       </c>
@@ -1973,23 +2182,31 @@
       <c r="K23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M23" s="6">
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="R23" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="S23" s="6">
         <v>21184453</v>
       </c>
-      <c r="N23" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T23" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="U23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>15</v>
       </c>
@@ -2021,23 +2238,31 @@
       <c r="K24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="M24" s="6">
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="R24" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="S24" s="6">
         <v>9476473</v>
       </c>
-      <c r="N24" s="6">
+      <c r="T24" s="6">
         <v>4126598879</v>
       </c>
-      <c r="O24" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>16</v>
       </c>
@@ -2070,24 +2295,31 @@
       <c r="K25" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L25" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="M25" s="6">
-        <f>M26</f>
-        <v>13967944</v>
-      </c>
-      <c r="N25" s="6">
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="S25" s="6">
+        <v>9865646</v>
+      </c>
+      <c r="T25" s="6">
         <v>4169190429</v>
       </c>
-      <c r="O25" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U25" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="V25" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>17</v>
       </c>
@@ -2125,26 +2357,34 @@
       <c r="K26" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L26" s="6" t="str">
-        <f>L27</f>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="R26" s="30" t="str">
+        <f>R27</f>
         <v xml:space="preserve">AVENDAÑO GOMEZ YONELA </v>
       </c>
-      <c r="M26" s="6">
+      <c r="S26" s="6">
         <v>13967944</v>
       </c>
-      <c r="N26" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P26" s="8" t="str">
-        <f>P27</f>
+      <c r="T26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V26" s="8" t="str">
+        <f>V27</f>
         <v>avendanoyonela@gmail.com</v>
       </c>
-      <c r="Q26" s="10"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="W26" s="10"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>18</v>
       </c>
@@ -2158,7 +2398,9 @@
       <c r="E27" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="G27" s="6">
         <v>19</v>
       </c>
@@ -2174,73 +2416,98 @@
       <c r="K27" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>78</v>
-      </c>
+      <c r="L27" s="6"/>
       <c r="M27" s="6"/>
-      <c r="N27" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="O27" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="10"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="10"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="S27" s="6">
+        <v>13967944</v>
+      </c>
+      <c r="T27" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V27" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="10"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="10"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S30" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="M8:M9"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="R8:R9"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="D8:D9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="S8:S9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Matricula_5to_grado.xlsx
+++ b/Matricula_5to_grado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF95052-17D9-41E8-B094-4B9B0B9844D3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54192B4-F868-48BA-B5EA-1CA3E17A78EB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="134">
   <si>
     <t xml:space="preserve">APELLIDOS </t>
   </si>
@@ -435,7 +435,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,29 +452,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -609,85 +619,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1270,11 +1281,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:W30"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="5" width="25.42578125" customWidth="1"/>
@@ -1284,12 +1295,12 @@
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="7.85546875" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="2.5703125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="3.7109375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="4.7109375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="3.5703125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="2.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="32.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="2.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="2.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32.7109375" style="1" customWidth="1"/>
     <col min="18" max="18" width="40.5703125" customWidth="1"/>
     <col min="19" max="19" width="18.5703125" customWidth="1"/>
     <col min="20" max="20" width="17.28515625" customWidth="1"/>
@@ -1298,1203 +1309,1711 @@
     <col min="23" max="23" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C4" s="1" t="s">
+    <row r="1" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+    </row>
+    <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C5" s="1" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="F6" s="1" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="J6" t="s">
+      <c r="H6" s="4"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="26"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="21" t="s">
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="21" t="s">
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="S8" s="21" t="s">
+      <c r="S8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="T8" s="21" t="s">
+      <c r="T8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="21" t="s">
+      <c r="U8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="V8" s="21" t="s">
+      <c r="V8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="W8" s="3"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22" t="s">
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17" t="s">
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22">
+      <c r="R9" s="14"/>
+      <c r="S9" s="14">
         <v>19421428</v>
       </c>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="3"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>1</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6">
+      <c r="B10" s="17"/>
+      <c r="C10" s="18">
         <v>36028714</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="18">
         <v>24</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="18">
         <v>11</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="18">
         <v>2013</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="18">
         <v>12</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29" t="s">
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="18">
         <v>13648370</v>
       </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6" t="s">
+      <c r="T10" s="18"/>
+      <c r="U10" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="V10" s="8"/>
-    </row>
-    <row r="11" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="V10" s="21"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <v>2</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6">
+      <c r="B11" s="17"/>
+      <c r="C11" s="18">
         <v>36438664</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="18">
         <v>22</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="18">
         <v>12</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="18">
         <v>2014</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="22">
         <v>10</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6" t="s">
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="R11" s="6" t="s">
+      <c r="R11" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="S11" s="6">
+      <c r="S11" s="18">
         <v>18310473</v>
       </c>
-      <c r="T11" s="6" t="s">
+      <c r="T11" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="U11" s="6" t="s">
+      <c r="U11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="V11" s="8" t="s">
+      <c r="V11" s="21" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <v>3</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="6">
+      <c r="B12" s="17"/>
+      <c r="C12" s="18">
         <v>39737493</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="18">
         <v>7</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="18">
         <v>6</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="18">
         <v>2015</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="18">
         <v>10</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6" t="s">
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="18">
         <v>11955213</v>
       </c>
-      <c r="T12" s="6" t="s">
+      <c r="T12" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="U12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="V12" s="6" t="s">
+      <c r="V12" s="18" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>4</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="6">
+      <c r="B13" s="17"/>
+      <c r="C13" s="18">
         <v>36867490</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="18">
         <v>16</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="18">
         <v>10</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="18">
         <v>2015</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="18">
         <v>9</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6" t="s">
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R13" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="18">
         <v>25560862</v>
       </c>
-      <c r="T13" s="6" t="s">
+      <c r="T13" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="U13" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V13" s="8" t="s">
+      <c r="V13" s="21" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>5</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="6">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18">
         <v>37007653</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="18">
         <v>12</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="18">
         <v>6</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="18">
         <v>2015</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="18">
         <v>10</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6" t="s">
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="S14" s="6">
+      <c r="S14" s="18">
         <v>22655606</v>
       </c>
-      <c r="T14" s="6">
+      <c r="T14" s="18">
         <v>4120296760</v>
       </c>
-      <c r="U14" s="6" t="s">
+      <c r="U14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="9" t="s">
+      <c r="V14" s="23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <v>6</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="6">
+      <c r="B15" s="17"/>
+      <c r="C15" s="18">
         <v>37163621</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="18">
         <v>11</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="18">
         <v>7</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="18">
         <v>2013</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="18">
         <v>12</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6" t="s">
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="R15" s="6" t="s">
+      <c r="R15" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="S15" s="6">
+      <c r="S15" s="18">
         <v>22655626</v>
       </c>
-      <c r="T15" s="6" t="s">
+      <c r="T15" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="U15" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V15" s="8"/>
-      <c r="W15" s="10"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="V15" s="21"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <v>7</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="6">
+      <c r="B16" s="17"/>
+      <c r="C16" s="18">
         <v>37195819</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="18">
         <v>15</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="18">
         <v>9</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="18">
         <v>2015</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="18">
         <v>10</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6" t="s">
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="S16" s="6">
+      <c r="S16" s="18">
         <v>20434036</v>
       </c>
-      <c r="T16" s="7" t="s">
+      <c r="T16" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U16" s="6" t="s">
+      <c r="U16" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V16" s="8" t="s">
+      <c r="V16" s="21" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>8</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="6">
+      <c r="B17" s="17"/>
+      <c r="C17" s="18">
         <v>37302814</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="18">
         <v>10</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="18">
         <v>11</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="18">
         <v>2015</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="18">
         <v>9</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6" t="s">
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="R17" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S17" s="18">
         <v>25643421</v>
       </c>
-      <c r="T17" s="6" t="s">
+      <c r="T17" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="U17" s="6" t="s">
+      <c r="U17" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V17" s="8" t="s">
+      <c r="V17" s="21" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="6">
+      <c r="B18" s="17"/>
+      <c r="C18" s="18">
         <v>37302829</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="18">
         <v>29</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="18">
         <v>11</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="18">
         <v>2015</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="18">
         <v>9</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6" t="s">
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="R18" s="30" t="s">
+      <c r="R18" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="S18" s="6">
+      <c r="S18" s="18">
         <v>11460128</v>
       </c>
-      <c r="T18" s="6">
+      <c r="T18" s="18">
         <v>4125494832</v>
       </c>
-      <c r="U18" s="6" t="s">
+      <c r="U18" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="V18" s="8" t="s">
+      <c r="V18" s="21" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <v>10</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="6">
+      <c r="B19" s="17"/>
+      <c r="C19" s="18">
         <v>37302834</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="26">
         <v>13</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="26">
         <v>11</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="26">
         <v>2015</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="26">
         <v>9</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11" t="s">
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="R19" s="30" t="s">
+      <c r="R19" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="S19" s="6">
+      <c r="S19" s="18">
         <v>12123839</v>
       </c>
-      <c r="T19" s="6" t="s">
+      <c r="T19" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="U19" s="6" t="s">
+      <c r="U19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="V19" s="6" t="s">
+      <c r="V19" s="18" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
         <v>11</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="6">
+      <c r="B20" s="17"/>
+      <c r="C20" s="18">
         <v>37302837</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="18">
         <v>15</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="18">
         <v>9</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="18">
         <v>2015</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="18">
         <v>10</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6" t="s">
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="R20" s="30" t="s">
+      <c r="R20" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="S20" s="6">
+      <c r="S20" s="18">
         <v>22655269</v>
       </c>
-      <c r="T20" s="6" t="s">
+      <c r="T20" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="U20" s="6" t="s">
+      <c r="U20" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V20" s="8" t="s">
+      <c r="V20" s="21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
         <v>12</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="6">
+      <c r="B21" s="17"/>
+      <c r="C21" s="18">
         <v>37302853</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="26">
         <v>28</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="26">
         <v>11</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="26">
         <v>2015</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="26">
         <v>9</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11" t="s">
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="R21" s="30" t="s">
+      <c r="R21" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="S21" s="6">
+      <c r="S21" s="18">
         <v>17130994</v>
       </c>
-      <c r="T21" s="6">
+      <c r="T21" s="18">
         <v>4127693370</v>
       </c>
-      <c r="U21" s="6" t="s">
+      <c r="U21" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="V21" s="8" t="s">
+      <c r="V21" s="21" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
         <v>13</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="6">
+      <c r="B22" s="17"/>
+      <c r="C22" s="18">
         <v>37302862</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="18">
         <v>11</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="18">
         <v>10</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="18">
         <v>2015</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="18">
         <v>9</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6" t="s">
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="R22" s="30" t="s">
+      <c r="R22" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="S22" s="6">
+      <c r="S22" s="18">
         <v>17340678</v>
       </c>
-      <c r="T22" s="6" t="s">
+      <c r="T22" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="U22" s="6" t="s">
+      <c r="U22" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="V22" s="8" t="s">
+      <c r="V22" s="21" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
         <v>14</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="6">
+      <c r="B23" s="17"/>
+      <c r="C23" s="18">
         <v>37302821</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="18">
         <v>10</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="18">
         <v>9</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="18">
         <v>2015</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="18">
         <v>10</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6" t="s">
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="R23" s="30" t="s">
+      <c r="R23" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="S23" s="6">
+      <c r="S23" s="18">
         <v>21184453</v>
       </c>
-      <c r="T23" s="6" t="s">
+      <c r="T23" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="U23" s="6" t="s">
+      <c r="U23" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="V23" s="8" t="s">
+      <c r="V23" s="21" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>15</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="6">
+      <c r="B24" s="17"/>
+      <c r="C24" s="18">
         <v>11521184453</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="18">
         <v>20</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="18">
         <v>3</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="18">
         <v>2015</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="18">
         <v>10</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6" t="s">
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="R24" s="30" t="s">
+      <c r="R24" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="S24" s="6">
+      <c r="S24" s="18">
         <v>9476473</v>
       </c>
-      <c r="T24" s="6">
+      <c r="T24" s="18">
         <v>4126598879</v>
       </c>
-      <c r="U24" s="6" t="s">
+      <c r="U24" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V24" s="8" t="s">
+      <c r="V24" s="21" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
         <v>16</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="6">
+      <c r="B25" s="17"/>
+      <c r="C25" s="18">
         <v>1159476473</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="6" t="str">
+      <c r="F25" s="18" t="str">
         <f>F26</f>
         <v>Merida</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="18">
         <v>8</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="18">
         <v>10</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="18">
         <v>2015</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="18">
         <v>9</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6" t="s">
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="R25" s="12" t="s">
+      <c r="R25" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="S25" s="6">
+      <c r="S25" s="18">
         <v>9865646</v>
       </c>
-      <c r="T25" s="6">
+      <c r="T25" s="18">
         <v>4169190429</v>
       </c>
-      <c r="U25" s="6" t="s">
+      <c r="U25" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="V25" s="8" t="s">
+      <c r="V25" s="21" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
         <v>17</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="6">
+      <c r="B26" s="17"/>
+      <c r="C26" s="18">
         <f>C27</f>
         <v>11513967944</v>
       </c>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="17" t="str">
         <f>D27</f>
         <v>RODRIGUEZ AVENDAÑO</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="18">
         <f>G27</f>
         <v>19</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="18">
         <f>H27</f>
         <v>10</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="18">
         <f>I27</f>
         <v>2015</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="18">
         <f>J27</f>
         <v>9</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6" t="s">
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="R26" s="30" t="str">
+      <c r="R26" s="25" t="str">
         <f>R27</f>
         <v xml:space="preserve">AVENDAÑO GOMEZ YONELA </v>
       </c>
-      <c r="S26" s="6">
+      <c r="S26" s="18">
         <v>13967944</v>
       </c>
-      <c r="T26" s="6" t="s">
+      <c r="T26" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="U26" s="6" t="s">
+      <c r="U26" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V26" s="8" t="str">
+      <c r="V26" s="21" t="str">
         <f>V27</f>
         <v>avendanoyonela@gmail.com</v>
       </c>
-      <c r="W26" s="10"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="W26" s="24"/>
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="28">
         <v>18</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="6">
+      <c r="B27" s="28"/>
+      <c r="C27" s="18">
         <v>11513967944</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="18">
         <v>19</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="18">
         <v>10</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="18">
         <v>2015</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="18">
         <v>9</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6" t="s">
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="R27" s="6" t="s">
+      <c r="R27" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="S27" s="6">
+      <c r="S27" s="18">
         <v>13967944</v>
       </c>
-      <c r="T27" s="6" t="s">
+      <c r="T27" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="U27" s="6" t="s">
+      <c r="U27" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="V27" s="8" t="s">
+      <c r="V27" s="21" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="10"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="10"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S30" s="28"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+    </row>
+    <row r="41" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="S8:S9"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="R8:R9"/>
@@ -2502,12 +3021,6 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="S8:S9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Matricula_5to_grado.xlsx
+++ b/Matricula_5to_grado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54192B4-F868-48BA-B5EA-1CA3E17A78EB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F898B99D-D476-4C8F-AC99-B39151FBEC52}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="119">
   <si>
     <t xml:space="preserve">APELLIDOS </t>
   </si>
@@ -35,9 +35,6 @@
     <t>NOMBRES</t>
   </si>
   <si>
-    <t>EDAD</t>
-  </si>
-  <si>
     <t>GENERO</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t>TELEFONO</t>
   </si>
   <si>
-    <t xml:space="preserve">CORREO </t>
-  </si>
-  <si>
     <t>DIRECCIÓN</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t xml:space="preserve">V: </t>
   </si>
   <si>
-    <t xml:space="preserve">H: </t>
-  </si>
-  <si>
     <t>AÑO ESCOLAR 2025-2026</t>
   </si>
   <si>
@@ -218,9 +209,6 @@
     <t>F</t>
   </si>
   <si>
-    <t xml:space="preserve">AVENDAÑO GOMEZ YONELA </t>
-  </si>
-  <si>
     <t xml:space="preserve">CEDULA </t>
   </si>
   <si>
@@ -251,51 +239,6 @@
     <t xml:space="preserve">CALLE BOLIVAR </t>
   </si>
   <si>
-    <t>lisbethcastillo933@gmail.com</t>
-  </si>
-  <si>
-    <t>haimejpino@gmail,com</t>
-  </si>
-  <si>
-    <t>coromoto43gomez@gmail.com</t>
-  </si>
-  <si>
-    <t>pvirginiayenire@gmail.com</t>
-  </si>
-  <si>
-    <t>mariainma8@gmail.com</t>
-  </si>
-  <si>
-    <t>monicabarrioszerpa@gmail.com</t>
-  </si>
-  <si>
-    <t>dinardialarcon@gmail.com</t>
-  </si>
-  <si>
-    <t>alcidesjaimetrejo1146@gmail.com</t>
-  </si>
-  <si>
-    <t>milagrosmorin53@gmail.com</t>
-  </si>
-  <si>
-    <t>marieladennis912@gmail.com</t>
-  </si>
-  <si>
-    <t>yecenia19@gmail.com</t>
-  </si>
-  <si>
-    <t>sanchezanateri@gmail.com</t>
-  </si>
-  <si>
-    <t>elgatojeanp2309@gmail.com</t>
-  </si>
-  <si>
-    <t>norarangel07101967</t>
-  </si>
-  <si>
-    <t>avendanoyonela@gmail.com</t>
-  </si>
-  <si>
     <t>0412-7650706</t>
   </si>
   <si>
@@ -429,6 +372,18 @@
   </si>
   <si>
     <t>AVENDAÑO GOMEZ</t>
+  </si>
+  <si>
+    <t>Parentesco</t>
+  </si>
+  <si>
+    <t>MADRE</t>
+  </si>
+  <si>
+    <t>PADRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> YONELA </t>
   </si>
 </sst>
 </file>
@@ -439,14 +394,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -475,14 +422,20 @@
     <font>
       <u/>
       <sz val="12"/>
-      <color theme="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
@@ -495,7 +448,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -614,94 +567,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -875,7 +834,7 @@
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -943,16 +902,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>17690</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>131082</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2630715</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -982,8 +941,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5743575" y="85725"/>
-          <a:ext cx="3562350" cy="476250"/>
+          <a:off x="8794297" y="131082"/>
+          <a:ext cx="8396061" cy="503464"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1281,35 +1240,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="5" width="25.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="6" max="6" width="33.5703125" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="2.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="3.7109375" style="1" customWidth="1"/>
     <col min="14" max="14" width="4.7109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="3.5703125" style="1" customWidth="1"/>
     <col min="16" max="16" width="2.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="32.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="40.5703125" customWidth="1"/>
+    <col min="17" max="17" width="49" style="1" customWidth="1"/>
+    <col min="18" max="18" width="45.42578125" customWidth="1"/>
     <col min="19" max="19" width="18.5703125" customWidth="1"/>
     <col min="20" max="20" width="17.28515625" customWidth="1"/>
-    <col min="21" max="21" width="24.28515625" customWidth="1"/>
-    <col min="22" max="22" width="37.140625" customWidth="1"/>
-    <col min="23" max="23" width="34.85546875" customWidth="1"/>
+    <col min="21" max="21" width="30.28515625" customWidth="1"/>
+    <col min="22" max="22" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1333,9 +1291,8 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-    </row>
-    <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1359,9 +1316,8 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-    </row>
-    <row r="3" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1385,13 +1341,12 @@
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-    </row>
-    <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="2"/>
@@ -1413,13 +1368,12 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-    </row>
-    <row r="5" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="2"/>
@@ -1441,27 +1395,24 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-    </row>
-    <row r="6" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="2"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1475,13 +1426,12 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="2"/>
@@ -1503,1198 +1453,1135 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-    </row>
-    <row r="8" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    </row>
+    <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="T8" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="V8" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
+      <c r="K9" s="23"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23">
+        <v>19421428</v>
+      </c>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11">
+        <v>36028714</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11">
+        <v>24</v>
+      </c>
+      <c r="I10" s="11">
+        <v>11</v>
+      </c>
+      <c r="J10" s="11">
+        <v>2013</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="S10" s="11">
+        <v>13648370</v>
+      </c>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="V10" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W10" s="2"/>
+    </row>
+    <row r="11" spans="1:23" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>2</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11">
+        <v>36438664</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
+        <v>22</v>
+      </c>
+      <c r="I11" s="11">
+        <v>12</v>
+      </c>
+      <c r="J11" s="11">
+        <v>2014</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="S11" s="11">
+        <v>18310473</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="V11" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11">
+        <v>39737493</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="E12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11">
+        <v>7</v>
+      </c>
+      <c r="I12" s="11">
+        <v>6</v>
+      </c>
+      <c r="J12" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="S12" s="11">
+        <v>11955213</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V12" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>4</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11">
+        <v>36867490</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G13" s="11"/>
+      <c r="H13" s="11">
+        <v>16</v>
+      </c>
+      <c r="I13" s="11">
+        <v>10</v>
+      </c>
+      <c r="J13" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="S13" s="11">
+        <v>25560862</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V13" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11">
+        <v>37007653</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11">
+        <v>12</v>
+      </c>
+      <c r="I14" s="11">
+        <v>6</v>
+      </c>
+      <c r="J14" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="R14" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="S14" s="11">
+        <v>22655606</v>
+      </c>
+      <c r="T14" s="11">
+        <v>4120296760</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="V14" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>6</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11">
+        <v>37163621</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11">
+        <v>11</v>
+      </c>
+      <c r="I15" s="11">
+        <v>7</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2013</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="S15" s="11">
+        <v>22655626</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V15" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W15" s="2"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>7</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11">
+        <v>37195819</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11">
+        <v>15</v>
+      </c>
+      <c r="I16" s="11">
+        <v>9</v>
+      </c>
+      <c r="J16" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="S16" s="11">
+        <v>20434036</v>
+      </c>
+      <c r="T16" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V16" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W16" s="2"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <v>8</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="11">
+        <v>37302814</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11">
+        <v>10</v>
+      </c>
+      <c r="I17" s="11">
+        <v>11</v>
+      </c>
+      <c r="J17" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="R17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="S17" s="11">
+        <v>25643421</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V17" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>9</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11">
+        <v>37302829</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11">
+        <v>29</v>
+      </c>
+      <c r="I18" s="11">
+        <v>11</v>
+      </c>
+      <c r="J18" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="S18" s="11">
+        <v>11460128</v>
+      </c>
+      <c r="T18" s="11">
+        <v>4125494832</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="V18" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11">
+        <v>37302834</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="16">
+        <v>13</v>
+      </c>
+      <c r="I19" s="16">
+        <v>11</v>
+      </c>
+      <c r="J19" s="16">
+        <v>2015</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S19" s="11">
+        <v>12123839</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="V19" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11">
+        <v>37302837</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11">
+        <v>15</v>
+      </c>
+      <c r="I20" s="11">
+        <v>9</v>
+      </c>
+      <c r="J20" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="S20" s="11">
+        <v>22655269</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V20" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>12</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11">
+        <v>37302853</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="16">
+        <v>28</v>
+      </c>
+      <c r="I21" s="16">
+        <v>11</v>
+      </c>
+      <c r="J21" s="16">
+        <v>2015</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="R21" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="S21" s="11">
+        <v>17130994</v>
+      </c>
+      <c r="T21" s="11">
+        <v>4127693370</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="V21" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
+        <v>13</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11">
+        <v>37302862</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11">
+        <v>11</v>
+      </c>
+      <c r="I22" s="11">
+        <v>10</v>
+      </c>
+      <c r="J22" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="R22" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S22" s="11">
+        <v>17340678</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="V22" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <v>14</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11">
+        <v>37302821</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11">
+        <v>10</v>
+      </c>
+      <c r="I23" s="11">
+        <v>9</v>
+      </c>
+      <c r="J23" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="R23" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="S23" s="11">
+        <v>21184453</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="V23" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>15</v>
+      </c>
+      <c r="B24" s="11">
+        <v>11521184453</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11">
+        <v>20</v>
+      </c>
+      <c r="I24" s="11">
         <v>3</v>
       </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="7" t="s">
+      <c r="J24" s="11">
+        <v>2015</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="R24" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S24" s="11">
+        <v>9476473</v>
+      </c>
+      <c r="T24" s="11">
+        <v>4126598879</v>
+      </c>
+      <c r="U24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="T8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-    </row>
-    <row r="9" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14">
-        <v>19421428</v>
-      </c>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-    </row>
-    <row r="10" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
-        <v>1</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18">
-        <v>36028714</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="18">
-        <v>24</v>
-      </c>
-      <c r="H10" s="18">
-        <v>11</v>
-      </c>
-      <c r="I10" s="18">
-        <v>2013</v>
-      </c>
-      <c r="J10" s="18">
-        <v>12</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="S10" s="18">
-        <v>13648370</v>
-      </c>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="V10" s="21"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-    </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
-        <v>2</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18">
-        <v>36438664</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="18">
-        <v>22</v>
-      </c>
-      <c r="H11" s="18">
-        <v>12</v>
-      </c>
-      <c r="I11" s="18">
-        <v>2014</v>
-      </c>
-      <c r="J11" s="22">
-        <v>10</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="R11" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="S11" s="18">
-        <v>18310473</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="V11" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-    </row>
-    <row r="12" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
-        <v>3</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18">
-        <v>39737493</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="18">
-        <v>7</v>
-      </c>
-      <c r="H12" s="18">
-        <v>6</v>
-      </c>
-      <c r="I12" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J12" s="18">
-        <v>10</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="S12" s="18">
-        <v>11955213</v>
-      </c>
-      <c r="T12" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="U12" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="V12" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-    </row>
-    <row r="13" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
-        <v>4</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="18">
-        <v>36867490</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="18">
+      <c r="V24" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W24" s="2"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
         <v>16</v>
       </c>
-      <c r="H13" s="18">
-        <v>10</v>
-      </c>
-      <c r="I13" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J13" s="18">
-        <v>9</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="S13" s="18">
-        <v>25560862</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="U13" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V13" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-    </row>
-    <row r="14" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
-        <v>5</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="18">
-        <v>37007653</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="18">
-        <v>12</v>
-      </c>
-      <c r="H14" s="18">
-        <v>6</v>
-      </c>
-      <c r="I14" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J14" s="18">
-        <v>10</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="R14" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="S14" s="18">
-        <v>22655606</v>
-      </c>
-      <c r="T14" s="18">
-        <v>4120296760</v>
-      </c>
-      <c r="U14" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="V14" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-    </row>
-    <row r="15" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
-        <v>6</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18">
-        <v>37163621</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="18">
-        <v>11</v>
-      </c>
-      <c r="H15" s="18">
-        <v>7</v>
-      </c>
-      <c r="I15" s="18">
-        <v>2013</v>
-      </c>
-      <c r="J15" s="18">
-        <v>12</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="R15" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="S15" s="18">
-        <v>22655626</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="U15" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V15" s="21"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="2"/>
-    </row>
-    <row r="16" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="17">
-        <v>7</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18">
-        <v>37195819</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="18">
-        <v>15</v>
-      </c>
-      <c r="H16" s="18">
-        <v>9</v>
-      </c>
-      <c r="I16" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J16" s="18">
-        <v>10</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="R16" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="S16" s="18">
-        <v>20434036</v>
-      </c>
-      <c r="T16" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="U16" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V16" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-    </row>
-    <row r="17" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
-        <v>8</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18">
-        <v>37302814</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="18">
-        <v>10</v>
-      </c>
-      <c r="H17" s="18">
-        <v>11</v>
-      </c>
-      <c r="I17" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J17" s="18">
-        <v>9</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="R17" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="S17" s="18">
-        <v>25643421</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="U17" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V17" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-    </row>
-    <row r="18" spans="1:24" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
-        <v>9</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18">
-        <v>37302829</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="18">
-        <v>29</v>
-      </c>
-      <c r="H18" s="18">
-        <v>11</v>
-      </c>
-      <c r="I18" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J18" s="18">
-        <v>9</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="R18" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="S18" s="18">
-        <v>11460128</v>
-      </c>
-      <c r="T18" s="18">
-        <v>4125494832</v>
-      </c>
-      <c r="U18" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="V18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-    </row>
-    <row r="19" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
-        <v>10</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18">
-        <v>37302834</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="26">
-        <v>13</v>
-      </c>
-      <c r="H19" s="26">
-        <v>11</v>
-      </c>
-      <c r="I19" s="26">
-        <v>2015</v>
-      </c>
-      <c r="J19" s="26">
-        <v>9</v>
-      </c>
-      <c r="K19" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="R19" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="S19" s="18">
-        <v>12123839</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="U19" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="V19" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-    </row>
-    <row r="20" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
-        <v>11</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18">
-        <v>37302837</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="18">
-        <v>15</v>
-      </c>
-      <c r="H20" s="18">
-        <v>9</v>
-      </c>
-      <c r="I20" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J20" s="18">
-        <v>10</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="R20" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="S20" s="18">
-        <v>22655269</v>
-      </c>
-      <c r="T20" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="U20" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V20" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-    </row>
-    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
-        <v>12</v>
-      </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18">
-        <v>37302853</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="26">
-        <v>28</v>
-      </c>
-      <c r="H21" s="26">
-        <v>11</v>
-      </c>
-      <c r="I21" s="26">
-        <v>2015</v>
-      </c>
-      <c r="J21" s="26">
-        <v>9</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="R21" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="S21" s="18">
-        <v>17130994</v>
-      </c>
-      <c r="T21" s="18">
-        <v>4127693370</v>
-      </c>
-      <c r="U21" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="V21" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-    </row>
-    <row r="22" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
-        <v>13</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18">
-        <v>37302862</v>
-      </c>
-      <c r="D22" s="17" t="s">
+      <c r="B25" s="11">
+        <v>1159476473</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E25" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="18">
-        <v>11</v>
-      </c>
-      <c r="H22" s="18">
-        <v>10</v>
-      </c>
-      <c r="I22" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J22" s="18">
-        <v>9</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="R22" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="S22" s="18">
-        <v>17340678</v>
-      </c>
-      <c r="T22" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="U22" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="V22" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-    </row>
-    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
-        <v>14</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18">
-        <v>37302821</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="18">
-        <v>10</v>
-      </c>
-      <c r="H23" s="18">
-        <v>9</v>
-      </c>
-      <c r="I23" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J23" s="18">
-        <v>10</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="R23" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="S23" s="18">
-        <v>21184453</v>
-      </c>
-      <c r="T23" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="U23" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="V23" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-    </row>
-    <row r="24" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
-        <v>15</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18">
-        <v>11521184453</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="18">
-        <v>20</v>
-      </c>
-      <c r="H24" s="18">
-        <v>3</v>
-      </c>
-      <c r="I24" s="18">
-        <v>2015</v>
-      </c>
-      <c r="J24" s="18">
-        <v>10</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="R24" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="S24" s="18">
-        <v>9476473</v>
-      </c>
-      <c r="T24" s="18">
-        <v>4126598879</v>
-      </c>
-      <c r="U24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V24" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-    </row>
-    <row r="25" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
-        <v>16</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="18">
-        <v>1159476473</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="18" t="str">
+      <c r="F25" s="11" t="str">
         <f>F26</f>
         <v>Merida</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="11"/>
+      <c r="H25" s="11">
         <v>8</v>
       </c>
-      <c r="H25" s="18">
+      <c r="I25" s="11">
         <v>10</v>
       </c>
-      <c r="I25" s="18">
+      <c r="J25" s="11">
         <v>2015</v>
       </c>
-      <c r="J25" s="18">
-        <v>9</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="R25" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="S25" s="18">
+      <c r="K25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="R25" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="S25" s="11">
         <v>9865646</v>
       </c>
-      <c r="T25" s="18">
+      <c r="T25" s="11">
         <v>4169190429</v>
       </c>
-      <c r="U25" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V25" s="21" t="s">
-        <v>87</v>
+      <c r="U25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V25" s="29" t="s">
+        <v>116</v>
       </c>
       <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-    </row>
-    <row r="26" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+    </row>
+    <row r="26" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
         <v>17</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18">
-        <f>C27</f>
+      <c r="B26" s="11">
+        <f>B27</f>
         <v>11513967944</v>
       </c>
-      <c r="D26" s="17" t="str">
+      <c r="D26" s="10" t="str">
         <f>D27</f>
         <v>RODRIGUEZ AVENDAÑO</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26" s="18">
-        <f>G27</f>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11">
+        <f>H27</f>
         <v>19</v>
       </c>
-      <c r="H26" s="18">
-        <f>H27</f>
+      <c r="I26" s="11">
+        <f>I27</f>
         <v>10</v>
       </c>
-      <c r="I26" s="18">
-        <f>I27</f>
+      <c r="J26" s="11">
+        <f>J27</f>
         <v>2015</v>
       </c>
-      <c r="J26" s="18">
-        <f>J27</f>
-        <v>9</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="R26" s="25" t="str">
+      <c r="K26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="R26" s="15" t="str">
         <f>R27</f>
-        <v xml:space="preserve">AVENDAÑO GOMEZ YONELA </v>
-      </c>
-      <c r="S26" s="18">
+        <v xml:space="preserve"> YONELA </v>
+      </c>
+      <c r="S26" s="11">
         <v>13967944</v>
       </c>
-      <c r="T26" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="U26" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V26" s="21" t="str">
-        <f>V27</f>
-        <v>avendanoyonela@gmail.com</v>
-      </c>
-      <c r="W26" s="24"/>
-      <c r="X26" s="2"/>
-    </row>
-    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="28">
+      <c r="T26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V26" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="W26" s="2"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
         <v>18</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="18">
+      <c r="B27" s="11">
         <v>11513967944</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="18">
+      <c r="D27" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11">
         <v>19</v>
       </c>
-      <c r="H27" s="18">
+      <c r="I27" s="11">
         <v>10</v>
       </c>
-      <c r="I27" s="18">
+      <c r="J27" s="11">
         <v>2015</v>
       </c>
-      <c r="J27" s="18">
-        <v>9</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="R27" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="S27" s="18">
+      <c r="K27" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="R27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="S27" s="11">
         <v>13967944</v>
       </c>
-      <c r="T27" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="U27" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="V27" s="21" t="s">
-        <v>88</v>
+      <c r="T27" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V27" s="29" t="s">
+        <v>116</v>
       </c>
       <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-    </row>
-    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
+    </row>
+    <row r="28" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
       <c r="V28" s="31"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="2"/>
-    </row>
-    <row r="29" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="2"/>
-    </row>
-    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W28" s="14"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="14"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2713,14 +2600,13 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
-      <c r="S30" s="32"/>
+      <c r="S30" s="21"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-    </row>
-    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U30" s="14"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="14"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2741,12 +2627,11 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-    </row>
-    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U31" s="14"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="14"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2767,12 +2652,11 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-    </row>
-    <row r="33" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U32" s="14"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="14"/>
+    </row>
+    <row r="33" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2793,12 +2677,11 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-    </row>
-    <row r="34" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U33" s="14"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="14"/>
+    </row>
+    <row r="34" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2819,12 +2702,11 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-    </row>
-    <row r="35" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U34" s="14"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="14"/>
+    </row>
+    <row r="35" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2845,12 +2727,11 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
-    </row>
-    <row r="36" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U35" s="14"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="14"/>
+    </row>
+    <row r="36" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2871,12 +2752,11 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-    </row>
-    <row r="37" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+    </row>
+    <row r="37" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2897,12 +2777,11 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
-    </row>
-    <row r="38" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+    </row>
+    <row r="38" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2923,12 +2802,11 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-    </row>
-    <row r="39" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+    </row>
+    <row r="39" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2952,9 +2830,8 @@
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-    </row>
-    <row r="40" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2978,9 +2855,8 @@
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
-      <c r="X40" s="2"/>
-    </row>
-    <row r="41" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3004,23 +2880,21 @@
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
+  <mergeCells count="12">
     <mergeCell ref="V8:V9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="S8:S9"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="R8:R9"/>
-    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="D8:D9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="S8:S9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
